--- a/docs/Files/D5_Enviado.xlsx
+++ b/docs/Files/D5_Enviado.xlsx
@@ -10332,7 +10332,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16764161 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16764161 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16769588 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16769588 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16772357 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16772357 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16911810 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16911810 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16951353 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16951353 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16954929 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16954929 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16955200 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16955200 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16986501 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16986501 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17001041 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17001041 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17069937 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17069937 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17096781 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17096781 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17100008 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17100008 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17145831 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17145831 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17152587 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17152587 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17247435 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17247435 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17249263 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17249263 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17322588 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17322588 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17322913 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17322913 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17331677 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17331677 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17342112 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17342112 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17364976 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17364976 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17365324 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17365324 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374556 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374556 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17381442 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17381442 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17394759 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17394759 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17398081 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17398081 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17399797 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17399797 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17405824 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17405824 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17405825 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17405825 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17410783 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17410783 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412507 / nota 4001956307; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412507 criada pela nota 4001956307</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412728 / nota 5214664; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412728 criada pela nota 5214664</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17414017 / nota 4001908327; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17414017 criada pela nota 4001908327</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13556586 / nota 13438439; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13438439 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13569650 / nota 13194523; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13194523 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13626020 / nota 13175222; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13175222 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13675740 / nota 13324254; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13324254 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13866688 / nota 12830332; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 12830332 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13959181 / nota 13726094; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13726094 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13960017 / nota 13472301; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13472301 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 13988222 / nota 13640126; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13640126 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14176680 / nota 13640124; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13640124 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14249375 / nota 13703453; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13703453 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14251734 / nota 13455016; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13455016 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14301739 / nota 13876823; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13876823 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14316111 / nota 13627687; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13627687 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14317257 / nota 13627688; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13627688 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14317509 / nota 13627690; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13627690 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14317942 / nota 13622129; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13622129 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14325356 / nota 13627687; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13627687 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14326231 / nota 13622128; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13622128 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14326483 / nota 13876829; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13876829 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14483294 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14483294 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14485065 / nota 13601065; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 14485065 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14491918 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14491918 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13412,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14494762 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14494762 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14499042 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14499042 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14510358 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14510358 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14511861 / nota 14250292; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14250292 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13636,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14519906 / nota 13403891; nenhum registro foi criado</t>
+          <t>CRIOU: D5 14519906 criada pela nota 13403891</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14523071 / nota 13417303; nenhum registro foi criado</t>
+          <t>CRIOU: D5 14523071 criada pela nota 13417303</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14567020 / nota 13403873; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13403873 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 14716229 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 14716229 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14814665 / nota 14442880; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14442880 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14875221 / nota 14350230; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14350230 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14897906 / nota 12304530; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 12304530 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14924737 / nota 13681282; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13681282 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15045861 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15045861 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15095169 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15095169 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15393147 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15393147 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 15416108 / nota 14590198; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14590198 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15430795 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15430795 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 15434932 / nota 14590200; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 15434932 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 15522030 / nota 4578307; nenhum registro foi criado</t>
+          <t>CRIOU: D5 15522030 criada pela nota 4578307</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15534618 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15534618 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15564619 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15564619 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15564639 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15564639 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15692095 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15692095 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 15741763 / nota 13908519; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 13908519 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15959136 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15959136 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 16296485 / nota 15009026; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 16296485 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16314089 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16314089 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16435801 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16435801 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16443688 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16443688 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16473748 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16473748 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16483983 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16483983 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16525724 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16525724 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15204,7 +15204,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16825798 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16825798 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16887249 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16887249 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16901349 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16901349 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16921524 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16921524 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16940323 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16940323 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16967141 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16967141 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17064331 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17064331 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17208123 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17208123 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17241778 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17241778 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17245064 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17245064 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17251051 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17251051 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17261142 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17261142 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17285608 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17285608 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15932,7 +15932,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17297543 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17297543 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17299130 / nota 13056245; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17299130 criada pela nota 13056245</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17312010 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17312010 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17313812 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17313812 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360047 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360047 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360048 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360048 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360319 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360319 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16324,7 +16324,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360330 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360330 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17362094 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17362094 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17362270 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17362270 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17372669 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17372669 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17379543 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17379543 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16604,7 +16604,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17384602 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17384602 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17387340 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17387340 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17391468 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17391468 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16772,7 +16772,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17398582 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17398582 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17398732 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17398732 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17399909 / nota 16696471; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17399909 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17402635 / nota 13056233; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17402635 criada pela nota 13056233</t>
         </is>
       </c>
     </row>
@@ -16996,7 +16996,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17405331 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17405331 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17405442 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17405442 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17408228 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17408228 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17411490 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17411490 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16393726 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16393726 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16473657 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16473657 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16887301 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16887301 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16911763 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16911763 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16925365 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16925365 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16962160 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16962160 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17556,7 +17556,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16968674 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16968674 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16973037 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16973037 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17017321 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17017321 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019147 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019147 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019148 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019148 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019149 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019149 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019154 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019154 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019155 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019155 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019156 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019156 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019157 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019157 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019158 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019158 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17019159 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17019159 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020525 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020525 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020526 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020526 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020527 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020527 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020528 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020528 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020529 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020529 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020540 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020540 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020541 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020541 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18620,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020542 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020542 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020543 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020543 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020544 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020544 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020545 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020545 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18844,7 +18844,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17020546 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17020546 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021023 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021023 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021330 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021330 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021339 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021339 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021485 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021485 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021486 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021486 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021487 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021487 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021488 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021488 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19292,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17021489 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17021489 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17023195 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17023195 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17029120 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17029120 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19460,7 +19460,7 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17186034 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17186034 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17230816 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17230816 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17283218 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17283218 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17309448 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17309448 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17331562 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17331562 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17361195 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17361195 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17362237 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17362237 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17362239 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17362239 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17372295 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17372295 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374471 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374471 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17392221 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17392221 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17392230 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17392230 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20132,7 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17394790 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17394790 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397247 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397247 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397248 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397248 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397249 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397249 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397260 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397260 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17401910 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17401910 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20468,7 +20468,7 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402536 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402536 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20524,7 +20524,7 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402615 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402615 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17403048 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17403048 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406255 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406255 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406260 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406260 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17410781 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17410781 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20804,7 +20804,7 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15997856 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15997856 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16222118 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16222118 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16392106 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16392106 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16415514 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16415514 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16421751 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16421751 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21084,7 @@
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16427600 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16427600 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16437643 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16437643 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16480149 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16480149 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16490542 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16490542 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16490543 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16490543 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16561188 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16561188 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21420,7 +21420,7 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16561196 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16561196 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21476,7 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16571618 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16571618 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16615175 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16615175 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16718869 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16718869 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21644,7 +21644,7 @@
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16734704 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16734704 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16747732 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16747732 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21756,7 +21756,7 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16747737 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16747737 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21812,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16789888 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16789888 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16795491 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16795491 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16805838 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16805838 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -21980,7 +21980,7 @@
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16818371 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16818371 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16825907 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16825907 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16830205 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16830205 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22148,7 +22148,7 @@
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16864567 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16864567 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16865593 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16865593 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16921568 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16921568 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16966246 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16966246 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16969331 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16969331 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16979587 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16979587 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16987373 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16987373 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22540,7 +22540,7 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16988391 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16988391 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16994247 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16994247 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17007866 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17007866 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17032606 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17032606 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042318 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042318 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042402 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042402 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042403 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042403 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042404 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042404 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042407 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042407 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042660 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042660 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17042662 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17042662 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23156,7 +23156,7 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17047949 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17047949 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23212,7 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17051449 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17051449 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23268,7 +23268,7 @@
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17069672 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17069672 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17074909 / nota 15892687; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17074909 criada pela nota 15892687</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17081542 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17081542 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17083927 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17083927 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17085097 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17085097 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23548,7 +23548,7 @@
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17088465 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17088465 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23604,7 +23604,7 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17089816 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17089816 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17093486 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17093486 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17096809 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17096809 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23772,7 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17099134 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17099134 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17099143 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17099143 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17101050 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17101050 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17102126 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17102126 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -23996,7 +23996,7 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17114412 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17114412 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17114413 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17114413 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17118487 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17118487 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24164,7 +24164,7 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17118489 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17118489 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17123069 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17123069 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17127064 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17127064 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17127065 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17127065 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24388,7 +24388,7 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17135191 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17135191 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17135194 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17135194 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17138758 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17138758 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24556,7 +24556,7 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17145707 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17145707 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24612,7 +24612,7 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17145708 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17145708 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17145709 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17145709 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24724,7 +24724,7 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17149924 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17149924 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17152598 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17152598 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24836,7 +24836,7 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17153767 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17153767 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17156069 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17156069 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17157363 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17157363 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25004,7 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17162153 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17162153 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25060,7 +25060,7 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17169084 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17169084 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17173507 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17173507 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17175988 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17175988 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25228,7 +25228,7 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17180463 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17180463 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17181112 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17181112 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17186180 / nota 16612407; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17186180 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17196417 / nota 16282386; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17196417 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17197381 / nota 16593543; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17197381 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25508,7 +25508,7 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17198142 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17198142 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25564,7 +25564,7 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17198324 / nota 16282384; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17198324 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25620,7 +25620,7 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17207747 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17207747 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17208124 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17208124 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17208127 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17208127 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17209400 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17209400 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25844,7 +25844,7 @@
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17209428 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17209428 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17209466 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17209466 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -25956,7 +25956,7 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17210282 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17210282 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26012,7 +26012,7 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17211826 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17211826 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26068,7 +26068,7 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17212920 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17212920 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17213137 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17213137 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26180,7 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17213859 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17213859 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17214577 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17214577 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26292,7 +26292,7 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17214605 / nota 16641837; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17214605 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17218704 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17218704 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17219573 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17219573 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26460,7 +26460,7 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224653 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224653 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224654 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224654 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26572,7 +26572,7 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224655 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224655 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26628,7 +26628,7 @@
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224728 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224728 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224754 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224754 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26740,7 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224780 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224780 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17225442 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17225442 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26852,7 +26852,7 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17225800 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17225800 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26908,7 +26908,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17225804 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17225804 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17226204 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17226204 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27020,7 +27020,7 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17226205 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17226205 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17228119 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17228119 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17228290 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17228290 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27188,7 +27188,7 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17230815 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17230815 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17230841 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17230841 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27300,7 +27300,7 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17232587 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17232587 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27356,7 +27356,7 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17233125 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17233125 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27412,7 +27412,7 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17233457 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17233457 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17234389 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17234389 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17236248 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17236248 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27580,7 +27580,7 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17237258 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17237258 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17238805 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17238805 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17249915 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17249915 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27748,7 +27748,7 @@
       </c>
       <c r="T313" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17250605 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17250605 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17254461 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17254461 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="T315" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17256253 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17256253 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27916,7 +27916,7 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17258300 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17258300 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -27972,7 +27972,7 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17261675 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17261675 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28028,7 +28028,7 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17264364 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17264364 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28084,7 +28084,7 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17268029 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17268029 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28140,7 +28140,7 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17268530 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17268530 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17270813 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17270813 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28252,7 +28252,7 @@
       </c>
       <c r="T322" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17271109 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17271109 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="T323" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17271247 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17271247 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17273059 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17273059 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28420,7 +28420,7 @@
       </c>
       <c r="T325" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17273124 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17273124 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28476,7 +28476,7 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17274489 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17274489 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28532,7 +28532,7 @@
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17274534 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17274534 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17281642 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17281642 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28644,7 +28644,7 @@
       </c>
       <c r="T329" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17285026 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17285026 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28700,7 +28700,7 @@
       </c>
       <c r="T330" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17285068 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17285068 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28756,7 +28756,7 @@
       </c>
       <c r="T331" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17285284 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17285284 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="T332" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17285601 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17285601 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="T333" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17293824 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17293824 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="T334" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17293880 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17293880 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -28980,7 +28980,7 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17300578 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17300578 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29036,7 +29036,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17304695 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17304695 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29092,7 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17307775 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17307775 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29148,7 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17309354 / nota 14944242; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17309354 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29204,7 +29204,7 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17311813 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17311813 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29260,7 +29260,7 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17311990 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17311990 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17312006 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17312006 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29372,7 +29372,7 @@
       </c>
       <c r="T342" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17312011 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17312011 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29428,7 +29428,7 @@
       </c>
       <c r="T343" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17312012 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17312012 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29484,7 @@
       </c>
       <c r="T344" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17320316 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17320316 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="T345" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17321680 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17321680 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29596,7 +29596,7 @@
       </c>
       <c r="T346" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17322576 / nota 16397547; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17322576 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29652,7 +29652,7 @@
       </c>
       <c r="T347" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17322589 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17322589 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="T348" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17323367 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17323367 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29764,7 +29764,7 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17325205 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17325205 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="T350" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17329713 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17329713 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29876,7 +29876,7 @@
       </c>
       <c r="T351" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17329727 / nota 4001937356; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17329727 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="T352" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17331055 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17331055 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -29988,7 +29988,7 @@
       </c>
       <c r="T353" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334129 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334129 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="T354" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334143 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334143 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334186 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334186 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30156,7 +30156,7 @@
       </c>
       <c r="T356" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334223 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334223 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30212,7 +30212,7 @@
       </c>
       <c r="T357" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334537 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334537 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30268,7 +30268,7 @@
       </c>
       <c r="T358" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17334557 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17334557 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30324,7 +30324,7 @@
       </c>
       <c r="T359" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17336011 / nota 16282480; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17336011 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30380,7 +30380,7 @@
       </c>
       <c r="T360" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17336106 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17336106 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30436,7 @@
       </c>
       <c r="T361" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17336107 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17336107 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="T362" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17336108 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17336108 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30548,7 +30548,7 @@
       </c>
       <c r="T363" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17336109 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17336109 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="T364" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17337001 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17337001 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30660,7 +30660,7 @@
       </c>
       <c r="T365" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17338268 / nota 16282468; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17338268 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30716,7 +30716,7 @@
       </c>
       <c r="T366" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17338269 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17338269 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="T367" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17338304 / nota 16282468; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17338304 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30828,7 +30828,7 @@
       </c>
       <c r="T368" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17338306 / nota 16282468; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17338306 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30884,7 +30884,7 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17338320 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17338320 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="T370" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17338321 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17338321 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -30996,7 +30996,7 @@
       </c>
       <c r="T371" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17338326 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17338326 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="T372" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17342113 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17342113 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31108,7 +31108,7 @@
       </c>
       <c r="T373" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17344257 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17344257 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31164,7 +31164,7 @@
       </c>
       <c r="T374" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17344392 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17344392 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="T375" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17344527 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17344527 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31276,7 +31276,7 @@
       </c>
       <c r="T376" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17345694 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17345694 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="T377" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17348560 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17348560 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="T378" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17348561 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17348561 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="T379" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17348566 / nota 16420911; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17348566 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="T380" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17348624 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17348624 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="T381" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17348629 / nota 4001946423; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17348629 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31612,7 +31612,7 @@
       </c>
       <c r="T382" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17350950 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17350950 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31668,7 @@
       </c>
       <c r="T383" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351029 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351029 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31724,7 +31724,7 @@
       </c>
       <c r="T384" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351071 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351071 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="T385" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351078 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351078 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31836,7 +31836,7 @@
       </c>
       <c r="T386" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351145 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351145 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="T387" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351871 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351871 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -31948,7 +31948,7 @@
       </c>
       <c r="T388" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17354117 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17354117 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32004,7 +32004,7 @@
       </c>
       <c r="T389" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17354130 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17354130 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32060,7 @@
       </c>
       <c r="T390" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17355518 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17355518 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="T391" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17356787 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17356787 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32172,7 +32172,7 @@
       </c>
       <c r="T392" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17358362 / nota 4001909934; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17358362 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="T393" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360049 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360049 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32284,7 +32284,7 @@
       </c>
       <c r="T394" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17360331 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17360331 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32340,7 +32340,7 @@
       </c>
       <c r="T395" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17362238 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17362238 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="T396" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17364323 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17364323 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32452,7 +32452,7 @@
       </c>
       <c r="T397" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17364355 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17364355 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32508,7 +32508,7 @@
       </c>
       <c r="T398" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17364492 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17364492 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32564,7 +32564,7 @@
       </c>
       <c r="T399" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17366208 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17366208 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32620,7 +32620,7 @@
       </c>
       <c r="T400" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17366903 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17366903 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="T401" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17367005 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17367005 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32732,7 +32732,7 @@
       </c>
       <c r="T402" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17367067 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17367067 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32788,7 +32788,7 @@
       </c>
       <c r="T403" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17367297 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17367297 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="T404" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17369667 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17369667 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32900,7 +32900,7 @@
       </c>
       <c r="T405" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17369722 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17369722 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="T406" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17372266 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17372266 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="T407" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17373258 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17373258 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33068,7 +33068,7 @@
       </c>
       <c r="T408" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374532 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374532 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33124,7 +33124,7 @@
       </c>
       <c r="T409" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374591 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374591 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33180,7 +33180,7 @@
       </c>
       <c r="T410" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374592 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374592 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33236,7 +33236,7 @@
       </c>
       <c r="T411" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17378227 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17378227 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="T412" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17378228 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17378228 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="T413" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17381523 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17381523 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33404,7 +33404,7 @@
       </c>
       <c r="T414" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17381861 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17381861 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33460,7 +33460,7 @@
       </c>
       <c r="T415" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17390417 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17390417 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33516,7 @@
       </c>
       <c r="T416" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17391975 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17391975 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33572,7 +33572,7 @@
       </c>
       <c r="T417" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17392029 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17392029 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33628,7 +33628,7 @@
       </c>
       <c r="T418" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17392104 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17392104 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="T419" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17396611 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17396611 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33740,7 +33740,7 @@
       </c>
       <c r="T420" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397052 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397052 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33796,7 +33796,7 @@
       </c>
       <c r="T421" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397305 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397305 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="T422" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17397551 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17397551 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33908,7 +33908,7 @@
       </c>
       <c r="T423" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17399519 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17399519 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="T424" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17401081 / nota 16282443; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17401081 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34020,7 +34020,7 @@
       </c>
       <c r="T425" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402330 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402330 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="T426" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402561 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402561 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34132,7 +34132,7 @@
       </c>
       <c r="T427" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402636 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402636 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34188,7 +34188,7 @@
       </c>
       <c r="T428" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17402761 / nota 16282487; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17402761 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34244,7 +34244,7 @@
       </c>
       <c r="T429" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17402796 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17402796 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="T430" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17403045 / nota 16612453; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17403045 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="T431" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17403047 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17403047 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="T432" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17403862 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17403862 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34468,7 +34468,7 @@
       </c>
       <c r="T433" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406380 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406380 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34524,7 +34524,7 @@
       </c>
       <c r="T434" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17406403 / nota 16282419; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17406403 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34580,7 +34580,7 @@
       </c>
       <c r="T435" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17409072 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17409072 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34636,7 +34636,7 @@
       </c>
       <c r="T436" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17410236 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17410236 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34692,7 +34692,7 @@
       </c>
       <c r="T437" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17410237 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17410237 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34748,7 @@
       </c>
       <c r="T438" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17410238 / nota 4001966419; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17410238 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34804,7 @@
       </c>
       <c r="T439" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412242 / nota 4001951155; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412242 criada pela nota 4001951155</t>
         </is>
       </c>
     </row>
@@ -34860,7 +34860,7 @@
       </c>
       <c r="T440" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412726 / nota 4001961683; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17412726 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -34916,7 +34916,7 @@
       </c>
       <c r="T441" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415538 / nota 16281220; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415538 criada pela nota 16281220</t>
         </is>
       </c>
     </row>
@@ -34972,7 +34972,7 @@
       </c>
       <c r="T442" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415910 / nota 16804047; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415910 criada pela nota 16804047</t>
         </is>
       </c>
     </row>
@@ -35028,7 +35028,7 @@
       </c>
       <c r="T443" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17416154 / nota 5175077; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17416154 criada pela nota 5175077</t>
         </is>
       </c>
     </row>
@@ -35084,7 +35084,7 @@
       </c>
       <c r="T444" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17312008 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17312008 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="T445" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17375711 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17375711 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="T446" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17384600 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17384600 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="T447" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17399657 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17399657 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35308,7 +35308,7 @@
       </c>
       <c r="T448" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17400859 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17400859 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="T449" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14526362 / nota 4001566847; nenhum registro foi criado</t>
+          <t>CRIOU: D5 14526362 criada pela nota 4001566847</t>
         </is>
       </c>
     </row>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="T450" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14537121 / nota 14210529; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14210529 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -35476,7 +35476,7 @@
       </c>
       <c r="T451" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 14696018 / nota 14210027; nenhum registro foi criado</t>
+          <t>NAO_SUBIU: nota normalizada 14210027 nao encontrada em notes.note</t>
         </is>
       </c>
     </row>
@@ -35532,7 +35532,7 @@
       </c>
       <c r="T452" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 15398597 / nota 4609988; nenhum registro foi criado</t>
+          <t>CRIOU: D5 15398597 criada pela nota 4609988</t>
         </is>
       </c>
     </row>
@@ -35588,7 +35588,7 @@
       </c>
       <c r="T453" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15411723 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15411723 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35644,7 +35644,7 @@
       </c>
       <c r="T454" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15672289 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15672289 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35700,7 +35700,7 @@
       </c>
       <c r="T455" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 15672364 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 15672364 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35756,7 +35756,7 @@
       </c>
       <c r="T456" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16301972 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16301972 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35812,7 +35812,7 @@
       </c>
       <c r="T457" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16389857 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16389857 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="T458" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16619609 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16619609 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35924,7 +35924,7 @@
       </c>
       <c r="T459" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16783931 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16783931 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -35980,7 +35980,7 @@
       </c>
       <c r="T460" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16911762 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16911762 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36036,7 +36036,7 @@
       </c>
       <c r="T461" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17109523 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17109523 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36092,7 +36092,7 @@
       </c>
       <c r="T462" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17150912 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17150912 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36148,7 +36148,7 @@
       </c>
       <c r="T463" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17256285 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17256285 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36204,7 +36204,7 @@
       </c>
       <c r="T464" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17261148 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17261148 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36260,7 +36260,7 @@
       </c>
       <c r="T465" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17349305 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17349305 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="T466" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17349306 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17349306 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36372,7 +36372,7 @@
       </c>
       <c r="T467" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17398742 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17398742 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36428,7 +36428,7 @@
       </c>
       <c r="T468" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406404 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406404 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36484,7 +36484,7 @@
       </c>
       <c r="T469" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406405 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406405 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36540,7 +36540,7 @@
       </c>
       <c r="T470" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406418 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406418 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="T471" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17408227 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17408227 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36652,7 +36652,7 @@
       </c>
       <c r="T472" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17409484 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17409484 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="T473" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17409978 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17409978 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -36764,7 +36764,7 @@
       </c>
       <c r="T474" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412508 / nota 4001949293; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412508 criada pela nota 4001949293</t>
         </is>
       </c>
     </row>
@@ -36820,7 +36820,7 @@
       </c>
       <c r="T475" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412509 / nota 5262873; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412509 criada pela nota 5262873</t>
         </is>
       </c>
     </row>
@@ -36876,7 +36876,7 @@
       </c>
       <c r="T476" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17412727 / nota 14567000; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17412727 criada pela nota 14567000</t>
         </is>
       </c>
     </row>
@@ -36932,7 +36932,7 @@
       </c>
       <c r="T477" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17414954 / nota 14565748; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17414954 criada pela nota 14565748</t>
         </is>
       </c>
     </row>
@@ -36988,7 +36988,7 @@
       </c>
       <c r="T478" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415539 / nota 16529545; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415539 criada pela nota 16529545</t>
         </is>
       </c>
     </row>
@@ -37044,7 +37044,7 @@
       </c>
       <c r="T479" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415551 / nota 15916681; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415551 criada pela nota 15916681</t>
         </is>
       </c>
     </row>
@@ -37100,7 +37100,7 @@
       </c>
       <c r="T480" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16833498 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16833498 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37156,7 @@
       </c>
       <c r="T481" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 16940184 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 16940184 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="T482" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17083763 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17083763 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37268,7 +37268,7 @@
       </c>
       <c r="T483" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17083852 / nota 16446590; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17083852 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="T484" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17210280 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17210280 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="T485" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17224426 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17224426 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37436,7 +37436,7 @@
       </c>
       <c r="T486" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17297625 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17297625 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37492,7 +37492,7 @@
       </c>
       <c r="T487" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17300577 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17300577 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37548,7 +37548,7 @@
       </c>
       <c r="T488" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17306029 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17306029 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37604,7 +37604,7 @@
       </c>
       <c r="T489" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17321978 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17321978 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37660,7 +37660,7 @@
       </c>
       <c r="T490" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17322586 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17322586 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37716,7 +37716,7 @@
       </c>
       <c r="T491" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17325206 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17325206 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="T492" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17329728 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17329728 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37828,7 +37828,7 @@
       </c>
       <c r="T493" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17347157 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17347157 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37884,7 +37884,7 @@
       </c>
       <c r="T494" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17351346 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17351346 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="T495" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17374555 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17374555 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -37996,7 +37996,7 @@
       </c>
       <c r="T496" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17376765 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17376765 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="T497" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17376769 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17376769 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="T498" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17383240 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17383240 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38164,7 +38164,7 @@
       </c>
       <c r="T499" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17384355 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17384355 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38220,7 +38220,7 @@
       </c>
       <c r="T500" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17384588 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17384588 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38276,7 +38276,7 @@
       </c>
       <c r="T501" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17384593 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17384593 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38332,7 +38332,7 @@
       </c>
       <c r="T502" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17384601 / nota 5179163; nenhum registro foi criado</t>
+          <t>ATUALIZOU: D5 17384601 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38388,7 +38388,7 @@
       </c>
       <c r="T503" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17388422 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17388422 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38444,7 +38444,7 @@
       </c>
       <c r="T504" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17388423 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17388423 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38500,7 +38500,7 @@
       </c>
       <c r="T505" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17400601 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17400601 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38556,7 +38556,7 @@
       </c>
       <c r="T506" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17403046 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17403046 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38612,7 +38612,7 @@
       </c>
       <c r="T507" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17405306 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17405306 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38668,7 +38668,7 @@
       </c>
       <c r="T508" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17406292 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17406292 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38724,7 +38724,7 @@
       </c>
       <c r="T509" t="inlineStr">
         <is>
-          <t>ATUALIZOU: D5 17410782 atualizada sem criar ou duplicar registro</t>
+          <t>ATUALIZOU: D5 17410782 atualizada sem duplicar registro</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="T510" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17414953 / nota 4001957375; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17414953 criada pela nota 4001957375</t>
         </is>
       </c>
     </row>
@@ -38836,7 +38836,7 @@
       </c>
       <c r="T511" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415550 / nota 15130935; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415550 criada pela nota 15130935</t>
         </is>
       </c>
     </row>
@@ -38892,7 +38892,7 @@
       </c>
       <c r="T512" t="inlineStr">
         <is>
-          <t>NAO_SUBIU: registro FiveNote inexistente para D5 17415707 / nota 16149735; nenhum registro foi criado</t>
+          <t>CRIOU: D5 17415707 criada pela nota 16149735</t>
         </is>
       </c>
     </row>
